--- a/eduservices/tagetik/DEMO_SOCLE_2027BUD_V1.xlsx
+++ b/eduservices/tagetik/DEMO_SOCLE_2027BUD_V1.xlsx
@@ -587,12 +587,12 @@
       </c>
       <c r="T1" s="3" t="inlineStr">
         <is>
-          <t>DEP_ACQ</t>
+          <t>DEPENSE_ACQ</t>
         </is>
       </c>
       <c r="U1" s="3" t="inlineStr">
         <is>
-          <t>DEP_MARQUE</t>
+          <t>DEPENSE_MARQUE</t>
         </is>
       </c>
     </row>
